--- a/artfynd/A 53826-2024 artfynd.xlsx
+++ b/artfynd/A 53826-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61039231</v>
+        <v>61101485</v>
       </c>
       <c r="B2" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222776</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399002.3942645206</v>
+        <v>399090</v>
       </c>
       <c r="R2" t="n">
-        <v>6196976.623308439</v>
+        <v>6196912</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Har bara hittat den här. Inom ett område med mycket sälg.</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +763,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ask-sälgskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61101485</v>
+        <v>61104783</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399090.210205632</v>
+        <v>398958</v>
       </c>
       <c r="R3" t="n">
-        <v>6196911.781851073</v>
+        <v>6197026</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,21 +860,11 @@
           <t>2016-06-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-06-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,7 +881,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ask-sälgskog</t>
+          <t>sälgskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,37 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61215544</v>
+        <v>61215537</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398889.4592835855</v>
+        <v>398889</v>
       </c>
       <c r="R4" t="n">
-        <v>6197072.326649938</v>
+        <v>6197072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,24 +974,9 @@
           <t>2016-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>uppslag av småaskar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,37 +1017,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61215537</v>
+        <v>61215544</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1110,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398889.4592835855</v>
+        <v>398889</v>
       </c>
       <c r="R5" t="n">
-        <v>6197072.326649938</v>
+        <v>6197072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,19 +1088,14 @@
           <t>2016-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>uppslag av småaskar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,6 +1129,688 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>61215515</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gyabjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>399036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6196947</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Sälgskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>61105352</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gyabjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>398717</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6197184</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ek-bokskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>61107132</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gyabjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>398891</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6197057</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>61215513</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gyabjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>399036</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6196947</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Sälgskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>61107123</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gyabjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>398891</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6197057</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>61039231</v>
+      </c>
+      <c r="B11" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gyabjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>399002</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6196977</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stehag</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-05-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-05-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Har bara hittat den här. Inom ett område med mycket sälg.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus J Magnusson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Skånes Flora 2016 - 2026</t>
         </is>

--- a/artfynd/A 53826-2024 artfynd.xlsx
+++ b/artfynd/A 53826-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -786,6 +791,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61101485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61104783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61215537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61215544</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61215515</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61105352</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61107132</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61215513</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Skånes Flora 2016 - 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61107123</t>
         </is>
       </c>
     </row>
@@ -1815,8 +1865,25 @@
           <t>Skånes Flora 2016 - 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61039231</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>